--- a/BUT2/1-DOC/SemestreBUT2_DACS_complete.xlsx
+++ b/BUT2/1-DOC/SemestreBUT2_DACS_complete.xlsx
@@ -14,25 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="96" uniqueCount="70">
-  <si>
-    <t>UE1.1</t>
-  </si>
-  <si>
-    <t>UE1.2</t>
-  </si>
-  <si>
-    <t>UE1.3</t>
-  </si>
-  <si>
-    <t>UE1.4</t>
-  </si>
-  <si>
-    <t>UE1.5</t>
-  </si>
-  <si>
-    <t>UE1.6</t>
-  </si>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="96" uniqueCount="76">
   <si>
     <t>à remplir</t>
   </si>
@@ -224,6 +206,42 @@
   </si>
   <si>
     <t>R4.B.12</t>
+  </si>
+  <si>
+    <t>UE4.1</t>
+  </si>
+  <si>
+    <t>UE4.2</t>
+  </si>
+  <si>
+    <t>UE4.3</t>
+  </si>
+  <si>
+    <t>UE4.4</t>
+  </si>
+  <si>
+    <t>UE4.5</t>
+  </si>
+  <si>
+    <t>UE4.6</t>
+  </si>
+  <si>
+    <t>UE1</t>
+  </si>
+  <si>
+    <t>UE2</t>
+  </si>
+  <si>
+    <t>UE3</t>
+  </si>
+  <si>
+    <t>UE4</t>
+  </si>
+  <si>
+    <t>UE5</t>
+  </si>
+  <si>
+    <t>UE6</t>
   </si>
 </sst>
 </file>
@@ -851,9 +869,21 @@
     <xf numFmtId="2" fontId="0" fillId="0" borderId="17" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="25" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="26" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="27" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="28" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -861,18 +891,6 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="29" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="27" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="26" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="25" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -1189,93 +1207,93 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:19" ht="23.25" x14ac:dyDescent="0.25">
-      <c r="A1" s="59" t="s">
-        <v>11</v>
-      </c>
-      <c r="B1" s="59"/>
-      <c r="C1" s="59"/>
-      <c r="D1" s="59"/>
-      <c r="E1" s="59"/>
-      <c r="F1" s="59"/>
-      <c r="G1" s="59"/>
-      <c r="H1" s="59"/>
-      <c r="I1" s="59"/>
-      <c r="J1" s="59"/>
-      <c r="K1" s="59"/>
-      <c r="L1" s="59"/>
-      <c r="M1" s="59"/>
-      <c r="N1" s="59"/>
-      <c r="O1" s="59"/>
-      <c r="P1" s="59"/>
-      <c r="Q1" s="53"/>
+      <c r="A1" s="53" t="s">
+        <v>5</v>
+      </c>
+      <c r="B1" s="53"/>
+      <c r="C1" s="53"/>
+      <c r="D1" s="53"/>
+      <c r="E1" s="53"/>
+      <c r="F1" s="53"/>
+      <c r="G1" s="53"/>
+      <c r="H1" s="53"/>
+      <c r="I1" s="53"/>
+      <c r="J1" s="53"/>
+      <c r="K1" s="53"/>
+      <c r="L1" s="53"/>
+      <c r="M1" s="53"/>
+      <c r="N1" s="53"/>
+      <c r="O1" s="53"/>
+      <c r="P1" s="53"/>
+      <c r="Q1" s="54"/>
     </row>
     <row r="2" spans="1:19" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="53"/>
-      <c r="B2" s="53"/>
-      <c r="C2" s="53"/>
-      <c r="D2" s="53"/>
-      <c r="E2" s="53"/>
-      <c r="F2" s="53"/>
-      <c r="G2" s="53"/>
-      <c r="H2" s="53"/>
-      <c r="I2" s="53"/>
-      <c r="J2" s="53"/>
-      <c r="K2" s="53"/>
-      <c r="L2" s="53"/>
-      <c r="M2" s="53"/>
-      <c r="N2" s="53"/>
-      <c r="O2" s="53"/>
-      <c r="P2" s="53"/>
-      <c r="Q2" s="53"/>
+      <c r="A2" s="54"/>
+      <c r="B2" s="54"/>
+      <c r="C2" s="54"/>
+      <c r="D2" s="54"/>
+      <c r="E2" s="54"/>
+      <c r="F2" s="54"/>
+      <c r="G2" s="54"/>
+      <c r="H2" s="54"/>
+      <c r="I2" s="54"/>
+      <c r="J2" s="54"/>
+      <c r="K2" s="54"/>
+      <c r="L2" s="54"/>
+      <c r="M2" s="54"/>
+      <c r="N2" s="54"/>
+      <c r="O2" s="54"/>
+      <c r="P2" s="54"/>
+      <c r="Q2" s="54"/>
     </row>
     <row r="3" spans="1:19" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A3" s="53"/>
-      <c r="B3" s="53"/>
+      <c r="A3" s="54"/>
+      <c r="B3" s="54"/>
       <c r="C3" s="1" t="s">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="D3" s="3" t="s">
-        <v>53</v>
+        <v>47</v>
       </c>
       <c r="E3" s="4" t="s">
-        <v>54</v>
+        <v>48</v>
       </c>
       <c r="F3" s="4" t="s">
-        <v>55</v>
+        <v>49</v>
       </c>
       <c r="G3" s="4" t="s">
-        <v>56</v>
+        <v>50</v>
       </c>
       <c r="H3" s="4" t="s">
-        <v>57</v>
+        <v>51</v>
       </c>
       <c r="I3" s="5" t="s">
-        <v>58</v>
-      </c>
-      <c r="J3" s="53"/>
+        <v>52</v>
+      </c>
+      <c r="J3" s="54"/>
       <c r="K3" s="3" t="s">
-        <v>53</v>
+        <v>47</v>
       </c>
       <c r="L3" s="4" t="s">
-        <v>54</v>
+        <v>48</v>
       </c>
       <c r="M3" s="4" t="s">
-        <v>55</v>
+        <v>49</v>
       </c>
       <c r="N3" s="4" t="s">
-        <v>56</v>
+        <v>50</v>
       </c>
       <c r="O3" s="4" t="s">
-        <v>57</v>
+        <v>51</v>
       </c>
       <c r="P3" s="5" t="s">
-        <v>58</v>
-      </c>
-      <c r="Q3" s="53"/>
+        <v>52</v>
+      </c>
+      <c r="Q3" s="54"/>
     </row>
     <row r="4" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A4" s="53"/>
-      <c r="B4" s="53"/>
+      <c r="A4" s="54"/>
+      <c r="B4" s="54"/>
       <c r="C4" s="32"/>
       <c r="D4" s="39">
         <f>C4</f>
@@ -1301,21 +1319,21 @@
         <f>C4</f>
         <v>0</v>
       </c>
-      <c r="J4" s="53"/>
+      <c r="J4" s="54"/>
       <c r="K4" s="12"/>
       <c r="L4" s="13"/>
       <c r="M4" s="13"/>
       <c r="N4" s="13"/>
       <c r="O4" s="13"/>
       <c r="P4" s="14"/>
-      <c r="Q4" s="53"/>
+      <c r="Q4" s="54"/>
       <c r="S4" s="31" t="s">
-        <v>6</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5" spans="1:19" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A5" s="60"/>
-      <c r="B5" s="60"/>
+      <c r="A5" s="55"/>
+      <c r="B5" s="55"/>
       <c r="C5" s="37"/>
       <c r="D5" s="20">
         <f>(D4*K5)/K5</f>
@@ -1341,7 +1359,7 @@
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="J5" s="53"/>
+      <c r="J5" s="54"/>
       <c r="K5" s="17">
         <v>40</v>
       </c>
@@ -1360,38 +1378,38 @@
       <c r="P5" s="19">
         <v>40</v>
       </c>
-      <c r="Q5" s="53"/>
+      <c r="Q5" s="54"/>
     </row>
     <row r="6" spans="1:19" ht="14.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A6" s="1" t="s">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="C6" s="57"/>
-      <c r="D6" s="53"/>
-      <c r="E6" s="53"/>
-      <c r="F6" s="53"/>
-      <c r="G6" s="53"/>
-      <c r="H6" s="53"/>
-      <c r="I6" s="53"/>
-      <c r="J6" s="53"/>
-      <c r="K6" s="58"/>
-      <c r="L6" s="58"/>
-      <c r="M6" s="58"/>
-      <c r="N6" s="58"/>
-      <c r="O6" s="58"/>
-      <c r="P6" s="58"/>
-      <c r="Q6" s="53"/>
+      <c r="D6" s="54"/>
+      <c r="E6" s="54"/>
+      <c r="F6" s="54"/>
+      <c r="G6" s="54"/>
+      <c r="H6" s="54"/>
+      <c r="I6" s="54"/>
+      <c r="J6" s="54"/>
+      <c r="K6" s="56"/>
+      <c r="L6" s="56"/>
+      <c r="M6" s="56"/>
+      <c r="N6" s="56"/>
+      <c r="O6" s="56"/>
+      <c r="P6" s="56"/>
+      <c r="Q6" s="54"/>
     </row>
     <row r="7" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A7" s="1" t="s">
-        <v>29</v>
+        <v>23</v>
       </c>
       <c r="B7" s="32"/>
       <c r="C7" s="8" t="s">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="D7" s="25">
         <f>B7</f>
@@ -1411,7 +1429,7 @@
       </c>
       <c r="H7" s="27"/>
       <c r="I7" s="28"/>
-      <c r="J7" s="53"/>
+      <c r="J7" s="54"/>
       <c r="K7" s="12">
         <v>15</v>
       </c>
@@ -1426,15 +1444,15 @@
       </c>
       <c r="O7" s="13"/>
       <c r="P7" s="14"/>
-      <c r="Q7" s="53"/>
+      <c r="Q7" s="54"/>
     </row>
     <row r="8" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A8" s="1" t="s">
-        <v>30</v>
+        <v>24</v>
       </c>
       <c r="B8" s="32"/>
       <c r="C8" s="8" t="s">
-        <v>18</v>
+        <v>12</v>
       </c>
       <c r="D8" s="23">
         <f>B8</f>
@@ -1448,7 +1466,7 @@
       <c r="G8" s="6"/>
       <c r="H8" s="6"/>
       <c r="I8" s="26"/>
-      <c r="J8" s="53"/>
+      <c r="J8" s="54"/>
       <c r="K8" s="15">
         <v>10</v>
       </c>
@@ -1459,15 +1477,15 @@
       <c r="N8" s="1"/>
       <c r="O8" s="1"/>
       <c r="P8" s="16"/>
-      <c r="Q8" s="53"/>
+      <c r="Q8" s="54"/>
     </row>
     <row r="9" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A9" s="1" t="s">
-        <v>37</v>
+        <v>31</v>
       </c>
       <c r="B9" s="32"/>
       <c r="C9" s="8" t="s">
-        <v>19</v>
+        <v>13</v>
       </c>
       <c r="D9" s="23">
         <f>B9</f>
@@ -1484,7 +1502,7 @@
         <v>0</v>
       </c>
       <c r="I9" s="26"/>
-      <c r="J9" s="53"/>
+      <c r="J9" s="54"/>
       <c r="K9" s="15">
         <v>12</v>
       </c>
@@ -1497,15 +1515,15 @@
         <v>10</v>
       </c>
       <c r="P9" s="16"/>
-      <c r="Q9" s="53"/>
+      <c r="Q9" s="54"/>
     </row>
     <row r="10" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A10" s="1" t="s">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="B10" s="32"/>
       <c r="C10" s="8" t="s">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="D10" s="29">
         <f>B10</f>
@@ -1522,7 +1540,7 @@
         <f>B10</f>
         <v>0</v>
       </c>
-      <c r="J10" s="53"/>
+      <c r="J10" s="54"/>
       <c r="K10" s="15">
         <v>15</v>
       </c>
@@ -1535,15 +1553,15 @@
       <c r="P10" s="16">
         <v>5</v>
       </c>
-      <c r="Q10" s="53"/>
+      <c r="Q10" s="54"/>
     </row>
     <row r="11" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A11" s="1" t="s">
-        <v>31</v>
+        <v>25</v>
       </c>
       <c r="B11" s="32"/>
       <c r="C11" s="8" t="s">
-        <v>21</v>
+        <v>15</v>
       </c>
       <c r="D11" s="29"/>
       <c r="E11" s="6"/>
@@ -1554,7 +1572,7 @@
       <c r="G11" s="6"/>
       <c r="H11" s="6"/>
       <c r="I11" s="26"/>
-      <c r="J11" s="53"/>
+      <c r="J11" s="54"/>
       <c r="K11" s="15"/>
       <c r="L11" s="1"/>
       <c r="M11" s="1">
@@ -1563,15 +1581,15 @@
       <c r="N11" s="1"/>
       <c r="O11" s="1"/>
       <c r="P11" s="16"/>
-      <c r="Q11" s="53"/>
+      <c r="Q11" s="54"/>
     </row>
     <row r="12" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A12" s="1" t="s">
-        <v>32</v>
+        <v>26</v>
       </c>
       <c r="B12" s="32"/>
       <c r="C12" s="8" t="s">
-        <v>22</v>
+        <v>16</v>
       </c>
       <c r="D12" s="29"/>
       <c r="E12" s="38">
@@ -1585,7 +1603,7 @@
       <c r="G12" s="6"/>
       <c r="H12" s="6"/>
       <c r="I12" s="26"/>
-      <c r="J12" s="53"/>
+      <c r="J12" s="54"/>
       <c r="K12" s="15"/>
       <c r="L12" s="1">
         <v>5</v>
@@ -1596,15 +1614,15 @@
       <c r="N12" s="1"/>
       <c r="O12" s="1"/>
       <c r="P12" s="16"/>
-      <c r="Q12" s="53"/>
+      <c r="Q12" s="54"/>
     </row>
     <row r="13" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A13" s="1" t="s">
-        <v>33</v>
+        <v>27</v>
       </c>
       <c r="B13" s="32"/>
       <c r="C13" s="8" t="s">
-        <v>23</v>
+        <v>17</v>
       </c>
       <c r="D13" s="29"/>
       <c r="E13" s="6"/>
@@ -1615,7 +1633,7 @@
       </c>
       <c r="H13" s="6"/>
       <c r="I13" s="26"/>
-      <c r="J13" s="53"/>
+      <c r="J13" s="54"/>
       <c r="K13" s="15"/>
       <c r="L13" s="1"/>
       <c r="M13" s="1"/>
@@ -1624,15 +1642,15 @@
       </c>
       <c r="O13" s="1"/>
       <c r="P13" s="16"/>
-      <c r="Q13" s="53"/>
+      <c r="Q13" s="54"/>
     </row>
     <row r="14" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A14" s="1" t="s">
-        <v>34</v>
+        <v>28</v>
       </c>
       <c r="B14" s="32"/>
       <c r="C14" s="8" t="s">
-        <v>24</v>
+        <v>18</v>
       </c>
       <c r="D14" s="29"/>
       <c r="E14" s="6">
@@ -1646,7 +1664,7 @@
       </c>
       <c r="H14" s="6"/>
       <c r="I14" s="26"/>
-      <c r="J14" s="53"/>
+      <c r="J14" s="54"/>
       <c r="K14" s="15"/>
       <c r="L14" s="1">
         <v>17</v>
@@ -1657,15 +1675,15 @@
       </c>
       <c r="O14" s="1"/>
       <c r="P14" s="16"/>
-      <c r="Q14" s="53"/>
+      <c r="Q14" s="54"/>
     </row>
     <row r="15" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A15" s="1" t="s">
-        <v>35</v>
+        <v>29</v>
       </c>
       <c r="B15" s="32"/>
       <c r="C15" s="8" t="s">
-        <v>25</v>
+        <v>19</v>
       </c>
       <c r="D15" s="29"/>
       <c r="E15" s="6">
@@ -1682,7 +1700,7 @@
       </c>
       <c r="H15" s="6"/>
       <c r="I15" s="26"/>
-      <c r="J15" s="53"/>
+      <c r="J15" s="54"/>
       <c r="K15" s="15"/>
       <c r="L15" s="1">
         <v>10</v>
@@ -1695,15 +1713,15 @@
       </c>
       <c r="O15" s="1"/>
       <c r="P15" s="16"/>
-      <c r="Q15" s="53"/>
+      <c r="Q15" s="54"/>
     </row>
     <row r="16" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A16" s="1" t="s">
-        <v>36</v>
+        <v>30</v>
       </c>
       <c r="B16" s="32"/>
       <c r="C16" s="8" t="s">
-        <v>26</v>
+        <v>20</v>
       </c>
       <c r="D16" s="29"/>
       <c r="E16" s="6"/>
@@ -1720,7 +1738,7 @@
         <f>B16</f>
         <v>0</v>
       </c>
-      <c r="J16" s="53"/>
+      <c r="J16" s="54"/>
       <c r="K16" s="15"/>
       <c r="L16" s="1"/>
       <c r="M16" s="1"/>
@@ -1733,15 +1751,15 @@
       <c r="P16" s="16">
         <v>16</v>
       </c>
-      <c r="Q16" s="53"/>
+      <c r="Q16" s="54"/>
     </row>
     <row r="17" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A17" s="1" t="s">
-        <v>16</v>
+        <v>10</v>
       </c>
       <c r="B17" s="32"/>
       <c r="C17" s="8" t="s">
-        <v>27</v>
+        <v>21</v>
       </c>
       <c r="D17" s="23">
         <f>B17</f>
@@ -1758,7 +1776,7 @@
         <v>0</v>
       </c>
       <c r="I17" s="26"/>
-      <c r="J17" s="53"/>
+      <c r="J17" s="54"/>
       <c r="K17" s="15">
         <v>8</v>
       </c>
@@ -1771,15 +1789,15 @@
         <v>10</v>
       </c>
       <c r="P17" s="16"/>
-      <c r="Q17" s="53"/>
+      <c r="Q17" s="54"/>
     </row>
     <row r="18" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A18" s="1" t="s">
-        <v>40</v>
+        <v>34</v>
       </c>
       <c r="B18" s="32"/>
       <c r="C18" s="8" t="s">
-        <v>28</v>
+        <v>22</v>
       </c>
       <c r="D18" s="23"/>
       <c r="E18" s="6">
@@ -1799,7 +1817,7 @@
         <f>B18</f>
         <v>0</v>
       </c>
-      <c r="J18" s="53"/>
+      <c r="J18" s="54"/>
       <c r="K18" s="15"/>
       <c r="L18" s="1">
         <v>5</v>
@@ -1814,15 +1832,15 @@
       <c r="P18" s="16">
         <v>8</v>
       </c>
-      <c r="Q18" s="53"/>
+      <c r="Q18" s="54"/>
     </row>
     <row r="19" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A19" s="1" t="s">
-        <v>41</v>
+        <v>35</v>
       </c>
       <c r="B19" s="32"/>
       <c r="C19" s="8" t="s">
-        <v>38</v>
+        <v>32</v>
       </c>
       <c r="D19" s="29"/>
       <c r="E19" s="6"/>
@@ -1836,7 +1854,7 @@
         <f>B19</f>
         <v>0</v>
       </c>
-      <c r="J19" s="53"/>
+      <c r="J19" s="54"/>
       <c r="K19" s="15"/>
       <c r="L19" s="1"/>
       <c r="M19" s="1"/>
@@ -1847,15 +1865,15 @@
       <c r="P19" s="16">
         <v>16</v>
       </c>
-      <c r="Q19" s="53"/>
+      <c r="Q19" s="54"/>
     </row>
     <row r="20" spans="1:17" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A20" s="1" t="s">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="B20" s="32"/>
       <c r="C20" s="8" t="s">
-        <v>39</v>
+        <v>33</v>
       </c>
       <c r="D20" s="33"/>
       <c r="E20" s="34"/>
@@ -1866,7 +1884,7 @@
         <f>B20</f>
         <v>0</v>
       </c>
-      <c r="J20" s="53"/>
+      <c r="J20" s="54"/>
       <c r="K20" s="15"/>
       <c r="L20" s="1"/>
       <c r="M20" s="1"/>
@@ -1875,12 +1893,12 @@
       <c r="P20" s="16">
         <v>15</v>
       </c>
-      <c r="Q20" s="53"/>
+      <c r="Q20" s="54"/>
     </row>
     <row r="21" spans="1:17" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A21" s="54"/>
-      <c r="B21" s="54"/>
-      <c r="C21" s="56"/>
+      <c r="A21" s="58"/>
+      <c r="B21" s="58"/>
+      <c r="C21" s="60"/>
       <c r="D21" s="30">
         <f t="shared" ref="D21:I21" si="1">((K7*D7)+(K8*D8)+(K9*D9)+(K10*D10)+(D11*K11)+(K12*D12)+(K13*D13)+(K14*D14)+(K15*D15)+(K16*D16)+(K17*D17)+(K18*D18)+(K19*D19)+(K20*D20))/K21</f>
         <v>0</v>
@@ -1905,7 +1923,7 @@
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="J21" s="53"/>
+      <c r="J21" s="54"/>
       <c r="K21" s="17">
         <v>60</v>
       </c>
@@ -1924,11 +1942,11 @@
       <c r="P21" s="19">
         <v>60</v>
       </c>
-      <c r="Q21" s="53"/>
+      <c r="Q21" s="54"/>
     </row>
     <row r="22" spans="1:17" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A22" s="1" t="s">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="B22" s="6">
         <f>SUM(D22:I22)/6</f>
@@ -1959,7 +1977,7 @@
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="J22" s="53"/>
+      <c r="J22" s="54"/>
       <c r="K22" s="3">
         <v>100</v>
       </c>
@@ -1978,132 +1996,132 @@
       <c r="P22" s="5">
         <v>100</v>
       </c>
-      <c r="Q22" s="53"/>
+      <c r="Q22" s="54"/>
     </row>
     <row r="23" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A23" s="53"/>
-      <c r="B23" s="53"/>
-      <c r="C23" s="53"/>
-      <c r="D23" s="53"/>
-      <c r="E23" s="53"/>
-      <c r="F23" s="53"/>
-      <c r="G23" s="53"/>
-      <c r="H23" s="53"/>
-      <c r="I23" s="53"/>
-      <c r="J23" s="53"/>
-      <c r="K23" s="53"/>
-      <c r="L23" s="53"/>
-      <c r="M23" s="53"/>
-      <c r="N23" s="53"/>
-      <c r="O23" s="53"/>
-      <c r="P23" s="53"/>
-      <c r="Q23" s="53"/>
+      <c r="A23" s="54"/>
+      <c r="B23" s="54"/>
+      <c r="C23" s="54"/>
+      <c r="D23" s="54"/>
+      <c r="E23" s="54"/>
+      <c r="F23" s="54"/>
+      <c r="G23" s="54"/>
+      <c r="H23" s="54"/>
+      <c r="I23" s="54"/>
+      <c r="J23" s="54"/>
+      <c r="K23" s="54"/>
+      <c r="L23" s="54"/>
+      <c r="M23" s="54"/>
+      <c r="N23" s="54"/>
+      <c r="O23" s="54"/>
+      <c r="P23" s="54"/>
+      <c r="Q23" s="54"/>
     </row>
     <row r="24" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A24" s="53"/>
-      <c r="B24" s="53"/>
-      <c r="C24" s="53"/>
-      <c r="D24" s="53"/>
-      <c r="E24" s="53"/>
-      <c r="F24" s="53"/>
-      <c r="G24" s="53"/>
-      <c r="H24" s="53"/>
-      <c r="I24" s="53"/>
-      <c r="J24" s="53"/>
-      <c r="K24" s="53"/>
-      <c r="L24" s="53"/>
-      <c r="M24" s="53"/>
-      <c r="N24" s="53"/>
-      <c r="O24" s="53"/>
-      <c r="P24" s="53"/>
-      <c r="Q24" s="53"/>
+      <c r="A24" s="54"/>
+      <c r="B24" s="54"/>
+      <c r="C24" s="54"/>
+      <c r="D24" s="54"/>
+      <c r="E24" s="54"/>
+      <c r="F24" s="54"/>
+      <c r="G24" s="54"/>
+      <c r="H24" s="54"/>
+      <c r="I24" s="54"/>
+      <c r="J24" s="54"/>
+      <c r="K24" s="54"/>
+      <c r="L24" s="54"/>
+      <c r="M24" s="54"/>
+      <c r="N24" s="54"/>
+      <c r="O24" s="54"/>
+      <c r="P24" s="54"/>
+      <c r="Q24" s="54"/>
     </row>
     <row r="25" spans="1:17" ht="23.25" x14ac:dyDescent="0.25">
-      <c r="A25" s="59" t="s">
-        <v>12</v>
-      </c>
-      <c r="B25" s="59"/>
-      <c r="C25" s="59"/>
-      <c r="D25" s="59"/>
-      <c r="E25" s="59"/>
-      <c r="F25" s="59"/>
-      <c r="G25" s="59"/>
-      <c r="H25" s="59"/>
-      <c r="I25" s="59"/>
-      <c r="J25" s="59"/>
-      <c r="K25" s="59"/>
-      <c r="L25" s="59"/>
-      <c r="M25" s="59"/>
-      <c r="N25" s="59"/>
-      <c r="O25" s="59"/>
-      <c r="P25" s="59"/>
-      <c r="Q25" s="53"/>
+      <c r="A25" s="53" t="s">
+        <v>6</v>
+      </c>
+      <c r="B25" s="53"/>
+      <c r="C25" s="53"/>
+      <c r="D25" s="53"/>
+      <c r="E25" s="53"/>
+      <c r="F25" s="53"/>
+      <c r="G25" s="53"/>
+      <c r="H25" s="53"/>
+      <c r="I25" s="53"/>
+      <c r="J25" s="53"/>
+      <c r="K25" s="53"/>
+      <c r="L25" s="53"/>
+      <c r="M25" s="53"/>
+      <c r="N25" s="53"/>
+      <c r="O25" s="53"/>
+      <c r="P25" s="53"/>
+      <c r="Q25" s="54"/>
     </row>
     <row r="26" spans="1:17" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A26" s="42"/>
       <c r="B26" s="42"/>
-      <c r="C26" s="53"/>
-      <c r="D26" s="53"/>
-      <c r="E26" s="53"/>
-      <c r="F26" s="53"/>
-      <c r="G26" s="53"/>
-      <c r="H26" s="53"/>
-      <c r="I26" s="53"/>
-      <c r="J26" s="53"/>
-      <c r="K26" s="53"/>
-      <c r="L26" s="53"/>
-      <c r="M26" s="53"/>
-      <c r="N26" s="53"/>
-      <c r="O26" s="53"/>
-      <c r="P26" s="53"/>
-      <c r="Q26" s="53"/>
+      <c r="C26" s="54"/>
+      <c r="D26" s="54"/>
+      <c r="E26" s="54"/>
+      <c r="F26" s="54"/>
+      <c r="G26" s="54"/>
+      <c r="H26" s="54"/>
+      <c r="I26" s="54"/>
+      <c r="J26" s="54"/>
+      <c r="K26" s="54"/>
+      <c r="L26" s="54"/>
+      <c r="M26" s="54"/>
+      <c r="N26" s="54"/>
+      <c r="O26" s="54"/>
+      <c r="P26" s="54"/>
+      <c r="Q26" s="54"/>
     </row>
     <row r="27" spans="1:17" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A27" s="42"/>
       <c r="B27" s="42"/>
       <c r="D27" s="9" t="s">
-        <v>0</v>
+        <v>64</v>
       </c>
       <c r="E27" s="10" t="s">
-        <v>1</v>
+        <v>65</v>
       </c>
       <c r="F27" s="10" t="s">
-        <v>2</v>
+        <v>66</v>
       </c>
       <c r="G27" s="10" t="s">
-        <v>3</v>
+        <v>67</v>
       </c>
       <c r="H27" s="10" t="s">
-        <v>4</v>
+        <v>68</v>
       </c>
       <c r="I27" s="11" t="s">
-        <v>5</v>
-      </c>
-      <c r="J27" s="53"/>
+        <v>69</v>
+      </c>
+      <c r="J27" s="54"/>
       <c r="K27" s="9" t="s">
-        <v>0</v>
+        <v>64</v>
       </c>
       <c r="L27" s="10" t="s">
-        <v>1</v>
+        <v>65</v>
       </c>
       <c r="M27" s="10" t="s">
-        <v>2</v>
+        <v>66</v>
       </c>
       <c r="N27" s="10" t="s">
-        <v>3</v>
+        <v>67</v>
       </c>
       <c r="O27" s="10" t="s">
-        <v>4</v>
+        <v>68</v>
       </c>
       <c r="P27" s="11" t="s">
-        <v>5</v>
-      </c>
-      <c r="Q27" s="53"/>
+        <v>69</v>
+      </c>
+      <c r="Q27" s="54"/>
     </row>
     <row r="28" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A28" s="42"/>
       <c r="B28" s="1" t="s">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="C28" s="43"/>
       <c r="D28" s="25">
@@ -2130,7 +2148,7 @@
         <f>C28</f>
         <v>0</v>
       </c>
-      <c r="J28" s="53"/>
+      <c r="J28" s="54"/>
       <c r="K28" s="12">
         <v>15</v>
       </c>
@@ -2149,12 +2167,12 @@
       <c r="P28" s="14">
         <v>15</v>
       </c>
-      <c r="Q28" s="53"/>
+      <c r="Q28" s="54"/>
     </row>
     <row r="29" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A29" s="42"/>
       <c r="B29" s="1" t="s">
-        <v>60</v>
+        <v>54</v>
       </c>
       <c r="C29" s="43"/>
       <c r="D29" s="23">
@@ -2181,7 +2199,7 @@
         <f>C29</f>
         <v>0</v>
       </c>
-      <c r="J29" s="53"/>
+      <c r="J29" s="54"/>
       <c r="K29" s="15">
         <v>5</v>
       </c>
@@ -2200,12 +2218,12 @@
       <c r="P29" s="16">
         <v>5</v>
       </c>
-      <c r="Q29" s="53"/>
+      <c r="Q29" s="54"/>
     </row>
     <row r="30" spans="1:17" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A30" s="42"/>
       <c r="B30" s="1" t="s">
-        <v>59</v>
+        <v>53</v>
       </c>
       <c r="C30" s="43"/>
       <c r="D30" s="50">
@@ -2232,7 +2250,7 @@
         <f>C30</f>
         <v>0</v>
       </c>
-      <c r="J30" s="53"/>
+      <c r="J30" s="54"/>
       <c r="K30" s="17">
         <v>40</v>
       </c>
@@ -2251,7 +2269,7 @@
       <c r="P30" s="19">
         <v>40</v>
       </c>
-      <c r="Q30" s="53"/>
+      <c r="Q30" s="54"/>
     </row>
     <row r="31" spans="1:17" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A31" s="36"/>
@@ -2281,7 +2299,7 @@
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="J31" s="53"/>
+      <c r="J31" s="54"/>
       <c r="K31" s="47">
         <v>60</v>
       </c>
@@ -2300,38 +2318,38 @@
       <c r="P31" s="49">
         <v>60</v>
       </c>
-      <c r="Q31" s="53"/>
+      <c r="Q31" s="54"/>
     </row>
     <row r="32" spans="1:17" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A32" s="1" t="s">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="B32" s="1" t="s">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="C32" s="57"/>
-      <c r="D32" s="53"/>
-      <c r="E32" s="53"/>
-      <c r="F32" s="53"/>
-      <c r="G32" s="53"/>
-      <c r="H32" s="53"/>
-      <c r="I32" s="53"/>
-      <c r="J32" s="53"/>
-      <c r="K32" s="58"/>
-      <c r="L32" s="58"/>
-      <c r="M32" s="58"/>
-      <c r="N32" s="58"/>
-      <c r="O32" s="58"/>
-      <c r="P32" s="58"/>
-      <c r="Q32" s="53"/>
+      <c r="D32" s="54"/>
+      <c r="E32" s="54"/>
+      <c r="F32" s="54"/>
+      <c r="G32" s="54"/>
+      <c r="H32" s="54"/>
+      <c r="I32" s="54"/>
+      <c r="J32" s="54"/>
+      <c r="K32" s="56"/>
+      <c r="L32" s="56"/>
+      <c r="M32" s="56"/>
+      <c r="N32" s="56"/>
+      <c r="O32" s="56"/>
+      <c r="P32" s="56"/>
+      <c r="Q32" s="54"/>
     </row>
     <row r="33" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A33" s="1" t="s">
-        <v>44</v>
+        <v>38</v>
       </c>
       <c r="B33" s="32"/>
       <c r="C33" s="8" t="s">
-        <v>45</v>
+        <v>39</v>
       </c>
       <c r="D33" s="25">
         <f>$B33</f>
@@ -2348,7 +2366,7 @@
         <f>$B33</f>
         <v>0</v>
       </c>
-      <c r="J33" s="53"/>
+      <c r="J33" s="54"/>
       <c r="K33" s="12">
         <v>27</v>
       </c>
@@ -2361,15 +2379,15 @@
       <c r="P33" s="14">
         <v>4</v>
       </c>
-      <c r="Q33" s="53"/>
+      <c r="Q33" s="54"/>
     </row>
     <row r="34" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A34" s="1" t="s">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="B34" s="32"/>
       <c r="C34" s="8" t="s">
-        <v>46</v>
+        <v>40</v>
       </c>
       <c r="D34" s="23">
         <f>$B34</f>
@@ -2383,7 +2401,7 @@
         <v>0</v>
       </c>
       <c r="I34" s="26"/>
-      <c r="J34" s="53"/>
+      <c r="J34" s="54"/>
       <c r="K34" s="15">
         <v>13</v>
       </c>
@@ -2394,15 +2412,15 @@
         <v>13</v>
       </c>
       <c r="P34" s="16"/>
-      <c r="Q34" s="53"/>
+      <c r="Q34" s="54"/>
     </row>
     <row r="35" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A35" s="1" t="s">
-        <v>43</v>
+        <v>37</v>
       </c>
       <c r="B35" s="32"/>
       <c r="C35" s="8" t="s">
-        <v>47</v>
+        <v>41</v>
       </c>
       <c r="D35" s="29"/>
       <c r="E35" s="6"/>
@@ -2413,7 +2431,7 @@
       </c>
       <c r="H35" s="6"/>
       <c r="I35" s="26"/>
-      <c r="J35" s="53"/>
+      <c r="J35" s="54"/>
       <c r="K35" s="15"/>
       <c r="L35" s="1"/>
       <c r="M35" s="1"/>
@@ -2422,15 +2440,15 @@
       </c>
       <c r="O35" s="1"/>
       <c r="P35" s="16"/>
-      <c r="Q35" s="53"/>
+      <c r="Q35" s="54"/>
     </row>
     <row r="36" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A36" s="1" t="s">
-        <v>42</v>
+        <v>36</v>
       </c>
       <c r="B36" s="32"/>
       <c r="C36" s="8" t="s">
-        <v>48</v>
+        <v>42</v>
       </c>
       <c r="D36" s="29"/>
       <c r="E36" s="6">
@@ -2441,7 +2459,7 @@
       <c r="G36" s="6"/>
       <c r="H36" s="6"/>
       <c r="I36" s="26"/>
-      <c r="J36" s="53"/>
+      <c r="J36" s="54"/>
       <c r="K36" s="15"/>
       <c r="L36" s="1">
         <v>18</v>
@@ -2450,15 +2468,15 @@
       <c r="N36" s="1"/>
       <c r="O36" s="1"/>
       <c r="P36" s="16"/>
-      <c r="Q36" s="53"/>
+      <c r="Q36" s="54"/>
     </row>
     <row r="37" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A37" s="1" t="s">
-        <v>40</v>
+        <v>34</v>
       </c>
       <c r="B37" s="32"/>
       <c r="C37" s="8" t="s">
-        <v>49</v>
+        <v>43</v>
       </c>
       <c r="D37" s="29"/>
       <c r="E37" s="6">
@@ -2472,7 +2490,7 @@
         <f>$B37</f>
         <v>0</v>
       </c>
-      <c r="J37" s="53"/>
+      <c r="J37" s="54"/>
       <c r="K37" s="15"/>
       <c r="L37" s="1">
         <v>4</v>
@@ -2483,15 +2501,15 @@
       <c r="P37" s="16">
         <v>13</v>
       </c>
-      <c r="Q37" s="53"/>
+      <c r="Q37" s="54"/>
     </row>
     <row r="38" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A38" s="1" t="s">
-        <v>52</v>
+        <v>46</v>
       </c>
       <c r="B38" s="32"/>
       <c r="C38" s="8" t="s">
-        <v>50</v>
+        <v>44</v>
       </c>
       <c r="D38" s="29"/>
       <c r="E38" s="6"/>
@@ -2505,7 +2523,7 @@
         <f>B38</f>
         <v>0</v>
       </c>
-      <c r="J38" s="53"/>
+      <c r="J38" s="54"/>
       <c r="K38" s="15"/>
       <c r="L38" s="1"/>
       <c r="M38" s="1"/>
@@ -2516,15 +2534,15 @@
       <c r="P38" s="16">
         <v>13</v>
       </c>
-      <c r="Q38" s="53"/>
+      <c r="Q38" s="54"/>
     </row>
     <row r="39" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A39" s="1" t="s">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="B39" s="32"/>
       <c r="C39" s="8" t="s">
-        <v>51</v>
+        <v>45</v>
       </c>
       <c r="D39" s="29"/>
       <c r="E39" s="6"/>
@@ -2535,7 +2553,7 @@
         <f>$B39</f>
         <v>0</v>
       </c>
-      <c r="J39" s="53"/>
+      <c r="J39" s="54"/>
       <c r="K39" s="15"/>
       <c r="L39" s="1"/>
       <c r="M39" s="1"/>
@@ -2544,15 +2562,15 @@
       <c r="P39" s="16">
         <v>10</v>
       </c>
-      <c r="Q39" s="53"/>
+      <c r="Q39" s="54"/>
     </row>
     <row r="40" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A40" s="1" t="s">
-        <v>62</v>
+        <v>56</v>
       </c>
       <c r="B40" s="32"/>
       <c r="C40" s="8" t="s">
-        <v>65</v>
+        <v>59</v>
       </c>
       <c r="D40" s="29"/>
       <c r="E40" s="6"/>
@@ -2563,7 +2581,7 @@
       <c r="G40" s="6"/>
       <c r="H40" s="6"/>
       <c r="I40" s="26"/>
-      <c r="J40" s="53"/>
+      <c r="J40" s="54"/>
       <c r="K40" s="15"/>
       <c r="L40" s="1"/>
       <c r="M40" s="1">
@@ -2572,15 +2590,15 @@
       <c r="N40" s="1"/>
       <c r="O40" s="1"/>
       <c r="P40" s="16"/>
-      <c r="Q40" s="53"/>
+      <c r="Q40" s="54"/>
     </row>
     <row r="41" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A41" s="1" t="s">
-        <v>61</v>
+        <v>55</v>
       </c>
       <c r="B41" s="32"/>
       <c r="C41" s="8" t="s">
-        <v>66</v>
+        <v>60</v>
       </c>
       <c r="D41" s="29"/>
       <c r="E41" s="6">
@@ -2594,7 +2612,7 @@
         <v>0</v>
       </c>
       <c r="I41" s="26"/>
-      <c r="J41" s="53"/>
+      <c r="J41" s="54"/>
       <c r="K41" s="15"/>
       <c r="L41" s="1">
         <v>7</v>
@@ -2605,15 +2623,15 @@
         <v>27</v>
       </c>
       <c r="P41" s="16"/>
-      <c r="Q41" s="53"/>
+      <c r="Q41" s="54"/>
     </row>
     <row r="42" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A42" s="1" t="s">
-        <v>35</v>
+        <v>29</v>
       </c>
       <c r="B42" s="32"/>
       <c r="C42" s="8" t="s">
-        <v>67</v>
+        <v>61</v>
       </c>
       <c r="D42" s="23"/>
       <c r="E42" s="6">
@@ -2630,7 +2648,7 @@
       </c>
       <c r="H42" s="6"/>
       <c r="I42" s="26"/>
-      <c r="J42" s="53"/>
+      <c r="J42" s="54"/>
       <c r="K42" s="15"/>
       <c r="L42" s="1">
         <v>11</v>
@@ -2643,15 +2661,15 @@
       </c>
       <c r="O42" s="1"/>
       <c r="P42" s="16"/>
-      <c r="Q42" s="53"/>
+      <c r="Q42" s="54"/>
     </row>
     <row r="43" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A43" s="1" t="s">
-        <v>64</v>
+        <v>58</v>
       </c>
       <c r="B43" s="32"/>
       <c r="C43" s="8" t="s">
-        <v>68</v>
+        <v>62</v>
       </c>
       <c r="D43" s="29"/>
       <c r="E43" s="6"/>
@@ -2662,7 +2680,7 @@
       <c r="G43" s="6"/>
       <c r="H43" s="6"/>
       <c r="I43" s="26"/>
-      <c r="J43" s="53"/>
+      <c r="J43" s="54"/>
       <c r="K43" s="15"/>
       <c r="L43" s="1"/>
       <c r="M43" s="1">
@@ -2671,15 +2689,15 @@
       <c r="N43" s="1"/>
       <c r="O43" s="1"/>
       <c r="P43" s="16"/>
-      <c r="Q43" s="53"/>
+      <c r="Q43" s="54"/>
     </row>
     <row r="44" spans="1:17" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A44" s="1" t="s">
-        <v>63</v>
+        <v>57</v>
       </c>
       <c r="B44" s="32"/>
       <c r="C44" s="8" t="s">
-        <v>69</v>
+        <v>63</v>
       </c>
       <c r="D44" s="33"/>
       <c r="E44" s="34"/>
@@ -2690,7 +2708,7 @@
       <c r="G44" s="34"/>
       <c r="H44" s="34"/>
       <c r="I44" s="35"/>
-      <c r="J44" s="53"/>
+      <c r="J44" s="54"/>
       <c r="K44" s="15"/>
       <c r="L44" s="1"/>
       <c r="M44" s="1">
@@ -2699,12 +2717,12 @@
       <c r="N44" s="1"/>
       <c r="O44" s="1"/>
       <c r="P44" s="16"/>
-      <c r="Q44" s="53"/>
+      <c r="Q44" s="54"/>
     </row>
     <row r="45" spans="1:17" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A45" s="54"/>
-      <c r="B45" s="54"/>
-      <c r="C45" s="54"/>
+      <c r="A45" s="58"/>
+      <c r="B45" s="58"/>
+      <c r="C45" s="58"/>
       <c r="D45" s="30">
         <f t="shared" ref="D45:I45" si="4">((K33*D33)+(K34*D34)+(D35*K35)+(K36*D36)+(K37*D37)+(K38*D38)+(K39*D39)+(K40*D40)+(K41*D41)+(K42*D42)+(K43*D43)+(K44*D44))/K45</f>
         <v>0</v>
@@ -2729,7 +2747,7 @@
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="J45" s="53"/>
+      <c r="J45" s="54"/>
       <c r="K45" s="17">
         <v>40</v>
       </c>
@@ -2748,11 +2766,11 @@
       <c r="P45" s="19">
         <v>40</v>
       </c>
-      <c r="Q45" s="53"/>
+      <c r="Q45" s="54"/>
     </row>
     <row r="46" spans="1:17" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A46" s="1" t="s">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="B46" s="6">
         <f>SUM(D46:I46)/6</f>
@@ -2783,7 +2801,7 @@
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="J46" s="53"/>
+      <c r="J46" s="54"/>
       <c r="K46" s="3">
         <v>100</v>
       </c>
@@ -2802,159 +2820,159 @@
       <c r="P46" s="5">
         <v>100</v>
       </c>
-      <c r="Q46" s="53"/>
+      <c r="Q46" s="54"/>
     </row>
     <row r="47" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A47" s="53"/>
-      <c r="B47" s="53"/>
-      <c r="C47" s="53"/>
-      <c r="D47" s="53"/>
-      <c r="E47" s="53"/>
-      <c r="F47" s="53"/>
-      <c r="G47" s="53"/>
-      <c r="H47" s="53"/>
-      <c r="I47" s="53"/>
-      <c r="J47" s="53"/>
-      <c r="K47" s="53"/>
-      <c r="L47" s="53"/>
-      <c r="M47" s="53"/>
-      <c r="N47" s="53"/>
-      <c r="O47" s="53"/>
-      <c r="P47" s="53"/>
-      <c r="Q47" s="53"/>
+      <c r="A47" s="54"/>
+      <c r="B47" s="54"/>
+      <c r="C47" s="54"/>
+      <c r="D47" s="54"/>
+      <c r="E47" s="54"/>
+      <c r="F47" s="54"/>
+      <c r="G47" s="54"/>
+      <c r="H47" s="54"/>
+      <c r="I47" s="54"/>
+      <c r="J47" s="54"/>
+      <c r="K47" s="54"/>
+      <c r="L47" s="54"/>
+      <c r="M47" s="54"/>
+      <c r="N47" s="54"/>
+      <c r="O47" s="54"/>
+      <c r="P47" s="54"/>
+      <c r="Q47" s="54"/>
     </row>
     <row r="48" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A48" s="53"/>
-      <c r="B48" s="53"/>
-      <c r="C48" s="53"/>
-      <c r="D48" s="53"/>
-      <c r="E48" s="53"/>
-      <c r="F48" s="53"/>
-      <c r="G48" s="53"/>
-      <c r="H48" s="53"/>
-      <c r="I48" s="53"/>
-      <c r="J48" s="53"/>
-      <c r="K48" s="53"/>
-      <c r="L48" s="53"/>
-      <c r="M48" s="53"/>
-      <c r="N48" s="53"/>
-      <c r="O48" s="53"/>
-      <c r="P48" s="53"/>
-      <c r="Q48" s="53"/>
+      <c r="A48" s="54"/>
+      <c r="B48" s="54"/>
+      <c r="C48" s="54"/>
+      <c r="D48" s="54"/>
+      <c r="E48" s="54"/>
+      <c r="F48" s="54"/>
+      <c r="G48" s="54"/>
+      <c r="H48" s="54"/>
+      <c r="I48" s="54"/>
+      <c r="J48" s="54"/>
+      <c r="K48" s="54"/>
+      <c r="L48" s="54"/>
+      <c r="M48" s="54"/>
+      <c r="N48" s="54"/>
+      <c r="O48" s="54"/>
+      <c r="P48" s="54"/>
+      <c r="Q48" s="54"/>
     </row>
     <row r="49" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A49" s="53"/>
-      <c r="B49" s="53"/>
-      <c r="C49" s="53"/>
-      <c r="D49" s="53"/>
-      <c r="E49" s="53"/>
-      <c r="F49" s="53"/>
-      <c r="G49" s="53"/>
-      <c r="H49" s="53"/>
-      <c r="I49" s="53"/>
-      <c r="J49" s="53"/>
-      <c r="K49" s="53"/>
-      <c r="L49" s="53"/>
-      <c r="M49" s="53"/>
-      <c r="N49" s="53"/>
-      <c r="O49" s="53"/>
-      <c r="P49" s="53"/>
-      <c r="Q49" s="53"/>
+      <c r="A49" s="54"/>
+      <c r="B49" s="54"/>
+      <c r="C49" s="54"/>
+      <c r="D49" s="54"/>
+      <c r="E49" s="54"/>
+      <c r="F49" s="54"/>
+      <c r="G49" s="54"/>
+      <c r="H49" s="54"/>
+      <c r="I49" s="54"/>
+      <c r="J49" s="54"/>
+      <c r="K49" s="54"/>
+      <c r="L49" s="54"/>
+      <c r="M49" s="54"/>
+      <c r="N49" s="54"/>
+      <c r="O49" s="54"/>
+      <c r="P49" s="54"/>
+      <c r="Q49" s="54"/>
     </row>
     <row r="50" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A50" s="53"/>
-      <c r="B50" s="53"/>
-      <c r="C50" s="53"/>
-      <c r="D50" s="53"/>
-      <c r="E50" s="53"/>
-      <c r="F50" s="53"/>
-      <c r="G50" s="53"/>
-      <c r="H50" s="53"/>
-      <c r="I50" s="53"/>
-      <c r="J50" s="53"/>
-      <c r="K50" s="53"/>
-      <c r="L50" s="53"/>
-      <c r="M50" s="53"/>
-      <c r="N50" s="53"/>
-      <c r="O50" s="53"/>
-      <c r="P50" s="53"/>
-      <c r="Q50" s="53"/>
+      <c r="A50" s="54"/>
+      <c r="B50" s="54"/>
+      <c r="C50" s="54"/>
+      <c r="D50" s="54"/>
+      <c r="E50" s="54"/>
+      <c r="F50" s="54"/>
+      <c r="G50" s="54"/>
+      <c r="H50" s="54"/>
+      <c r="I50" s="54"/>
+      <c r="J50" s="54"/>
+      <c r="K50" s="54"/>
+      <c r="L50" s="54"/>
+      <c r="M50" s="54"/>
+      <c r="N50" s="54"/>
+      <c r="O50" s="54"/>
+      <c r="P50" s="54"/>
+      <c r="Q50" s="54"/>
     </row>
     <row r="51" spans="1:17" ht="23.25" x14ac:dyDescent="0.25">
-      <c r="A51" s="59" t="s">
-        <v>13</v>
-      </c>
-      <c r="B51" s="59"/>
-      <c r="C51" s="59"/>
-      <c r="D51" s="59"/>
-      <c r="E51" s="59"/>
-      <c r="F51" s="59"/>
-      <c r="G51" s="59"/>
-      <c r="H51" s="59"/>
-      <c r="I51" s="59"/>
-      <c r="J51" s="59"/>
-      <c r="K51" s="59"/>
-      <c r="L51" s="59"/>
-      <c r="M51" s="59"/>
-      <c r="N51" s="59"/>
-      <c r="O51" s="59"/>
-      <c r="P51" s="59"/>
-      <c r="Q51" s="53"/>
+      <c r="A51" s="53" t="s">
+        <v>7</v>
+      </c>
+      <c r="B51" s="53"/>
+      <c r="C51" s="53"/>
+      <c r="D51" s="53"/>
+      <c r="E51" s="53"/>
+      <c r="F51" s="53"/>
+      <c r="G51" s="53"/>
+      <c r="H51" s="53"/>
+      <c r="I51" s="53"/>
+      <c r="J51" s="53"/>
+      <c r="K51" s="53"/>
+      <c r="L51" s="53"/>
+      <c r="M51" s="53"/>
+      <c r="N51" s="53"/>
+      <c r="O51" s="53"/>
+      <c r="P51" s="53"/>
+      <c r="Q51" s="54"/>
     </row>
     <row r="52" spans="1:17" ht="24" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A52" s="55"/>
-      <c r="B52" s="55"/>
-      <c r="C52" s="55"/>
-      <c r="D52" s="55"/>
-      <c r="E52" s="55"/>
-      <c r="F52" s="55"/>
-      <c r="G52" s="55"/>
-      <c r="H52" s="55"/>
-      <c r="I52" s="55"/>
-      <c r="J52" s="55"/>
-      <c r="K52" s="55"/>
-      <c r="L52" s="55"/>
-      <c r="M52" s="55"/>
-      <c r="N52" s="55"/>
-      <c r="O52" s="55"/>
-      <c r="P52" s="55"/>
-      <c r="Q52" s="53"/>
+      <c r="A52" s="59"/>
+      <c r="B52" s="59"/>
+      <c r="C52" s="59"/>
+      <c r="D52" s="59"/>
+      <c r="E52" s="59"/>
+      <c r="F52" s="59"/>
+      <c r="G52" s="59"/>
+      <c r="H52" s="59"/>
+      <c r="I52" s="59"/>
+      <c r="J52" s="59"/>
+      <c r="K52" s="59"/>
+      <c r="L52" s="59"/>
+      <c r="M52" s="59"/>
+      <c r="N52" s="59"/>
+      <c r="O52" s="59"/>
+      <c r="P52" s="59"/>
+      <c r="Q52" s="54"/>
     </row>
     <row r="53" spans="1:17" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A53" s="53"/>
-      <c r="B53" s="53"/>
-      <c r="C53" s="53"/>
+      <c r="A53" s="54"/>
+      <c r="B53" s="54"/>
+      <c r="C53" s="54"/>
       <c r="D53" s="3" t="s">
-        <v>0</v>
+        <v>70</v>
       </c>
       <c r="E53" s="4" t="s">
-        <v>1</v>
+        <v>71</v>
       </c>
       <c r="F53" s="4" t="s">
-        <v>2</v>
+        <v>72</v>
       </c>
       <c r="G53" s="4" t="s">
-        <v>3</v>
+        <v>73</v>
       </c>
       <c r="H53" s="4" t="s">
-        <v>4</v>
+        <v>74</v>
       </c>
       <c r="I53" s="5" t="s">
-        <v>5</v>
-      </c>
-      <c r="J53" s="53"/>
-      <c r="K53" s="53"/>
-      <c r="L53" s="53"/>
-      <c r="M53" s="53"/>
-      <c r="N53" s="53"/>
-      <c r="O53" s="53"/>
-      <c r="P53" s="53"/>
-      <c r="Q53" s="53"/>
+        <v>75</v>
+      </c>
+      <c r="J53" s="54"/>
+      <c r="K53" s="54"/>
+      <c r="L53" s="54"/>
+      <c r="M53" s="54"/>
+      <c r="N53" s="54"/>
+      <c r="O53" s="54"/>
+      <c r="P53" s="54"/>
+      <c r="Q53" s="54"/>
     </row>
     <row r="54" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A54" s="53"/>
-      <c r="B54" s="53"/>
-      <c r="C54" s="53"/>
+      <c r="A54" s="54"/>
+      <c r="B54" s="54"/>
+      <c r="C54" s="54"/>
       <c r="D54" s="1">
         <f t="shared" ref="D54:I54" si="6">(D46+D22)/2</f>
         <v>0</v>
@@ -2979,60 +2997,55 @@
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
-      <c r="J54" s="53"/>
-      <c r="K54" s="53"/>
-      <c r="L54" s="53"/>
-      <c r="M54" s="53"/>
-      <c r="N54" s="53"/>
-      <c r="O54" s="53"/>
-      <c r="P54" s="53"/>
-      <c r="Q54" s="53"/>
+      <c r="J54" s="54"/>
+      <c r="K54" s="54"/>
+      <c r="L54" s="54"/>
+      <c r="M54" s="54"/>
+      <c r="N54" s="54"/>
+      <c r="O54" s="54"/>
+      <c r="P54" s="54"/>
+      <c r="Q54" s="54"/>
     </row>
     <row r="55" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A55" s="53"/>
-      <c r="B55" s="53"/>
-      <c r="C55" s="53"/>
-      <c r="D55" s="53"/>
-      <c r="E55" s="53"/>
-      <c r="F55" s="53"/>
-      <c r="G55" s="53"/>
-      <c r="H55" s="53"/>
-      <c r="I55" s="53"/>
-      <c r="J55" s="53"/>
-      <c r="K55" s="53"/>
-      <c r="L55" s="53"/>
-      <c r="M55" s="53"/>
-      <c r="N55" s="53"/>
-      <c r="O55" s="53"/>
-      <c r="P55" s="53"/>
-      <c r="Q55" s="53"/>
+      <c r="A55" s="54"/>
+      <c r="B55" s="54"/>
+      <c r="C55" s="54"/>
+      <c r="D55" s="54"/>
+      <c r="E55" s="54"/>
+      <c r="F55" s="54"/>
+      <c r="G55" s="54"/>
+      <c r="H55" s="54"/>
+      <c r="I55" s="54"/>
+      <c r="J55" s="54"/>
+      <c r="K55" s="54"/>
+      <c r="L55" s="54"/>
+      <c r="M55" s="54"/>
+      <c r="N55" s="54"/>
+      <c r="O55" s="54"/>
+      <c r="P55" s="54"/>
+      <c r="Q55" s="54"/>
     </row>
     <row r="56" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A56" s="53"/>
-      <c r="B56" s="53"/>
-      <c r="C56" s="53"/>
-      <c r="D56" s="53"/>
-      <c r="E56" s="53"/>
-      <c r="F56" s="53"/>
-      <c r="G56" s="53"/>
-      <c r="H56" s="53"/>
-      <c r="I56" s="53"/>
-      <c r="J56" s="53"/>
-      <c r="K56" s="53"/>
-      <c r="L56" s="53"/>
-      <c r="M56" s="53"/>
-      <c r="N56" s="53"/>
-      <c r="O56" s="53"/>
-      <c r="P56" s="53"/>
-      <c r="Q56" s="53"/>
+      <c r="A56" s="54"/>
+      <c r="B56" s="54"/>
+      <c r="C56" s="54"/>
+      <c r="D56" s="54"/>
+      <c r="E56" s="54"/>
+      <c r="F56" s="54"/>
+      <c r="G56" s="54"/>
+      <c r="H56" s="54"/>
+      <c r="I56" s="54"/>
+      <c r="J56" s="54"/>
+      <c r="K56" s="54"/>
+      <c r="L56" s="54"/>
+      <c r="M56" s="54"/>
+      <c r="N56" s="54"/>
+      <c r="O56" s="54"/>
+      <c r="P56" s="54"/>
+      <c r="Q56" s="54"/>
     </row>
   </sheetData>
   <mergeCells count="21">
-    <mergeCell ref="A51:P51"/>
-    <mergeCell ref="J3:J22"/>
-    <mergeCell ref="A2:B5"/>
-    <mergeCell ref="K6:P6"/>
-    <mergeCell ref="C6:I6"/>
     <mergeCell ref="Q1:Q56"/>
     <mergeCell ref="A47:P50"/>
     <mergeCell ref="A45:C45"/>
@@ -3049,6 +3062,11 @@
     <mergeCell ref="K32:P32"/>
     <mergeCell ref="A1:P1"/>
     <mergeCell ref="A25:P25"/>
+    <mergeCell ref="A51:P51"/>
+    <mergeCell ref="J3:J22"/>
+    <mergeCell ref="A2:B5"/>
+    <mergeCell ref="K6:P6"/>
+    <mergeCell ref="C6:I6"/>
   </mergeCells>
   <conditionalFormatting sqref="D22:I22">
     <cfRule type="colorScale" priority="5">
